--- a/selenium_model/API_TEST_350_REPORT.xlsx
+++ b/selenium_model/API_TEST_350_REPORT.xlsx
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F338" t="n">
